--- a/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T07:42:05+00:00</t>
+    <t>2026-09-09T11:20:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:20:12+00:00</t>
+    <t>2026-09-09T11:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:32:53+00:00</t>
+    <t>2026-09-09T15:02:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:02:15+00:00</t>
+    <t>2026-09-10T08:46:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T08:46:19+00:00</t>
+    <t>2026-09-10T08:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/complements-spec-ps-indiv/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T08:58:26+00:00</t>
+    <t>2026-09-10T09:47:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
